--- a/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_IREN BCBADAJOZ.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_IREN BCBADAJOZ.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:X13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,7 +619,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Á. MERLO</t>
+          <t>J. NWANKWO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -628,76 +628,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2676</v>
+        <v>-3.126</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2676</v>
+        <v>-3.4504</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.3244</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2676</v>
+        <v>-5.8965</v>
       </c>
       <c r="H3" t="n">
-        <v>1.23</v>
+        <v>-4.0136</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0375</v>
+        <v>-1.8828</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2676</v>
+        <v>-1.4438</v>
       </c>
       <c r="K3" t="n">
-        <v>1.23</v>
+        <v>-1.8153</v>
       </c>
       <c r="L3" t="n">
-        <v>3.0375</v>
+        <v>0.3716000000000002</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-4.4528</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-2.1983</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-2.2544</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.7799999999999998</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-4.8746</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>5.6546</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.7706</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0.4079</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.1783</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.2201</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.2758</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-2.0558</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. OSÉS BERNALDÉZ</t>
+          <t>J. KELLIER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -706,76 +706,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4376</v>
+        <v>-3.433600000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4376</v>
+        <v>0.6734</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-4.1069</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4376</v>
+        <v>-7.1331</v>
       </c>
       <c r="H4" t="n">
-        <v>0.615</v>
+        <v>-4.7454</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8225</v>
+        <v>-2.3878</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4376</v>
+        <v>-0.8187</v>
       </c>
       <c r="K4" t="n">
-        <v>0.615</v>
+        <v>-0.8347000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8225</v>
+        <v>0.0159999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-6.3146</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-3.9107</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-2.4037</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.9248</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.8997</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.265</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.8484</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.4166</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.4902</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.6185</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.1087</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. NWANKWO</t>
+          <t>A. MERLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -784,76 +784,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>-3.126</v>
+        <v>-3.7908</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.4504</v>
+        <v>-1.7646</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3244</v>
+        <v>-2.0263</v>
       </c>
       <c r="G5" t="n">
-        <v>-5.8965</v>
+        <v>-0.6586999999999998</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.0136</v>
+        <v>-2.9989</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.8828</v>
+        <v>2.3401</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.4438</v>
+        <v>5.029500000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.8153</v>
+        <v>0.8497999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3716000000000002</v>
+        <v>4.1795</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.4528</v>
+        <v>-5.6882</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.1983</v>
+        <v>-3.8487</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.2544</v>
+        <v>-1.8396</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7799999999999998</v>
+        <v>0.195</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.8746</v>
+        <v>-5.8495</v>
       </c>
       <c r="R5" t="n">
-        <v>5.6546</v>
+        <v>6.0445</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7706</v>
+        <v>-0.8869</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4079</v>
+        <v>-1.2231</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1783</v>
+        <v>0.3362</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2201</v>
+        <v>-2.4401</v>
       </c>
       <c r="W5" t="n">
-        <v>3.2758</v>
+        <v>0.2786</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.0558</v>
+        <v>-2.7187</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. KELLIER</t>
+          <t>U. RAZAQUE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -865,73 +865,73 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.433600000000001</v>
+        <v>-4.605</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6734</v>
+        <v>-5.8291</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.1069</v>
+        <v>1.2239</v>
       </c>
       <c r="G6" t="n">
-        <v>-7.1331</v>
+        <v>-9.265799999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.7454</v>
+        <v>-9.3064</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.3878</v>
+        <v>0.04049999999999998</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8187</v>
+        <v>-2.5555</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.8347000000000001</v>
+        <v>-2.3841</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0159999999999999</v>
+        <v>-0.1713999999999998</v>
       </c>
       <c r="M6" t="n">
-        <v>-6.3146</v>
+        <v>-6.7103</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.9107</v>
+        <v>-6.9223</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.4037</v>
+        <v>0.212</v>
       </c>
       <c r="P6" t="n">
-        <v>2.9248</v>
+        <v>-1.17</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9749</v>
+        <v>-8.7745</v>
       </c>
       <c r="R6" t="n">
-        <v>3.8997</v>
+        <v>7.6045</v>
       </c>
       <c r="S6" t="n">
-        <v>1.265</v>
+        <v>-1.5403</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8484</v>
+        <v>-2.7749</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4166</v>
+        <v>1.2346</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4902</v>
+        <v>7.3711</v>
       </c>
       <c r="W6" t="n">
-        <v>1.6185</v>
+        <v>8.2758</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1087</v>
+        <v>-0.9047000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>U. RAZAQUE</t>
+          <t>L. BRYAN JR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -943,73 +943,73 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.605</v>
+        <v>-5.2206</v>
       </c>
       <c r="E7" t="n">
-        <v>-5.8291</v>
+        <v>2.9933</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2239</v>
+        <v>-8.213899999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-9.265799999999999</v>
+        <v>-6.1744</v>
       </c>
       <c r="H7" t="n">
-        <v>-9.3064</v>
+        <v>-4.1908</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04049999999999998</v>
+        <v>-1.9837</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.5555</v>
+        <v>3.7892</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.3841</v>
+        <v>2.728</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1713999999999998</v>
+        <v>1.061</v>
       </c>
       <c r="M7" t="n">
-        <v>-6.7103</v>
+        <v>-9.9635</v>
       </c>
       <c r="N7" t="n">
-        <v>-6.9223</v>
+        <v>-6.918799999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>0.212</v>
+        <v>-3.0447</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.17</v>
+        <v>-0.195</v>
       </c>
       <c r="Q7" t="n">
-        <v>-8.7745</v>
+        <v>-5.8496</v>
       </c>
       <c r="R7" t="n">
-        <v>7.6045</v>
+        <v>5.654599999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5403</v>
+        <v>2.1593</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.7749</v>
+        <v>1.1679</v>
       </c>
       <c r="U7" t="n">
-        <v>1.2346</v>
+        <v>0.9914000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>7.3711</v>
+        <v>-1.0106</v>
       </c>
       <c r="W7" t="n">
-        <v>8.2758</v>
+        <v>3.8858</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9047000000000001</v>
+        <v>-4.8965</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. BRYAN JR</t>
+          <t>A. DIAZ FERREIRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1021,73 +1021,73 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.2206</v>
+        <v>-5.315399999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>2.9933</v>
+        <v>0.3526999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-8.213899999999999</v>
+        <v>-5.667999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-6.1744</v>
+        <v>-1.4173</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.1908</v>
+        <v>-0.3257</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.9837</v>
+        <v>-1.0916</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7892</v>
+        <v>1.2886</v>
       </c>
       <c r="K8" t="n">
-        <v>2.728</v>
+        <v>1.0456</v>
       </c>
       <c r="L8" t="n">
-        <v>1.061</v>
+        <v>0.243</v>
       </c>
       <c r="M8" t="n">
-        <v>-9.9635</v>
+        <v>-2.7059</v>
       </c>
       <c r="N8" t="n">
-        <v>-6.918799999999999</v>
+        <v>-1.3713</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.0447</v>
+        <v>-1.3346</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.195</v>
+        <v>-1.9498</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.8496</v>
+        <v>-2.9248</v>
       </c>
       <c r="R8" t="n">
-        <v>5.654599999999999</v>
+        <v>0.975</v>
       </c>
       <c r="S8" t="n">
-        <v>2.1593</v>
+        <v>-0.5023</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1679</v>
+        <v>-0.4513</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9914000000000001</v>
+        <v>-0.05120000000000002</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0106</v>
+        <v>-1.4457</v>
       </c>
       <c r="W8" t="n">
-        <v>3.8858</v>
+        <v>2.4402</v>
       </c>
       <c r="X8" t="n">
-        <v>-4.8965</v>
+        <v>-3.8859</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. DIAZ FERREIRA</t>
+          <t>S. IDRIS IGENE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1099,73 +1099,73 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.315399999999999</v>
+        <v>-5.9276</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3526999999999999</v>
+        <v>-5.3602</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.667999999999999</v>
+        <v>-0.5673999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4173</v>
+        <v>-5.036300000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3257</v>
+        <v>-3.525</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0916</v>
+        <v>-1.5112</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2886</v>
+        <v>-2.0558</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0456</v>
+        <v>-0.9132999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>0.243</v>
+        <v>-1.1425</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.7059</v>
+        <v>-2.9805</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3713</v>
+        <v>-2.6118</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3346</v>
+        <v>-0.3687</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.9498</v>
+        <v>0.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9248</v>
+        <v>-3.8997</v>
       </c>
       <c r="R9" t="n">
-        <v>0.975</v>
+        <v>4.6797</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5023</v>
+        <v>-1.0083</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4513</v>
+        <v>-0.2403999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.05120000000000002</v>
+        <v>-0.7678999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4457</v>
+        <v>-0.663</v>
       </c>
       <c r="W9" t="n">
-        <v>2.4402</v>
+        <v>0.8357000000000001</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.8859</v>
+        <v>-1.4987</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. IDRIS IGENE</t>
+          <t>A. DEL CERRO MARTIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1177,73 +1177,73 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.9276</v>
+        <v>-6.411899999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.3602</v>
+        <v>-0.9021999999999997</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5673999999999999</v>
+        <v>-5.5096</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.036300000000001</v>
+        <v>-6.7471</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.525</v>
+        <v>-3.2706</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5112</v>
+        <v>-3.4765</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.0558</v>
+        <v>1.8634</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9132999999999999</v>
+        <v>2.6904</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1425</v>
+        <v>-0.8269999999999997</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.9805</v>
+        <v>-8.6105</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.6118</v>
+        <v>-5.9608</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3687</v>
+        <v>-2.6496</v>
       </c>
       <c r="P10" t="n">
-        <v>0.78</v>
+        <v>3.5098</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.8997</v>
+        <v>-1.9499</v>
       </c>
       <c r="R10" t="n">
-        <v>4.6797</v>
+        <v>5.4597</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0083</v>
+        <v>1.3237</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2403999999999999</v>
+        <v>0.2844999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7678999999999999</v>
+        <v>1.0392</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.663</v>
+        <v>-4.4981</v>
       </c>
       <c r="W10" t="n">
-        <v>0.8357000000000001</v>
+        <v>-1.1003</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4987</v>
+        <v>-3.3979</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. DEL CERRO MARTIN</t>
+          <t>P. OSES BERNALDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1252,76 +1252,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.411899999999999</v>
+        <v>-10.6306</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9021999999999997</v>
+        <v>-3.0377</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.5096</v>
+        <v>-7.5929</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.7471</v>
+        <v>-4.3743</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.2706</v>
+        <v>-4.005100000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.4765</v>
+        <v>-0.3692000000000002</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8634</v>
+        <v>1.0329</v>
       </c>
       <c r="K11" t="n">
-        <v>2.6904</v>
+        <v>-0.7163</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.8269999999999997</v>
+        <v>1.7491</v>
       </c>
       <c r="M11" t="n">
-        <v>-8.6105</v>
+        <v>-5.4071</v>
       </c>
       <c r="N11" t="n">
-        <v>-5.9608</v>
+        <v>-3.2888</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.6496</v>
+        <v>-2.1183</v>
       </c>
       <c r="P11" t="n">
-        <v>3.5098</v>
+        <v>-3.1197</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9499</v>
+        <v>-6.8245</v>
       </c>
       <c r="R11" t="n">
-        <v>5.4597</v>
+        <v>3.7048</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3237</v>
+        <v>0.9243</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2844999999999999</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0392</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-4.4981</v>
+        <v>-4.0607</v>
       </c>
       <c r="W11" t="n">
-        <v>-1.1003</v>
+        <v>2.6658</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.3979</v>
+        <v>-6.7264</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. MERLO</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1333,73 +1333,73 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.058399999999999</v>
+        <v>-11.3385</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.0322</v>
+        <v>-8.863799999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0263</v>
+        <v>-2.4747</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.9265</v>
+        <v>-9.319000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.229</v>
+        <v>-6.2523</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6976</v>
+        <v>-3.0668</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7618</v>
+        <v>-4.1608</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3802000000000001</v>
+        <v>-2.1434</v>
       </c>
       <c r="L12" t="n">
-        <v>1.142</v>
+        <v>-2.0174</v>
       </c>
       <c r="M12" t="n">
-        <v>-5.6882</v>
+        <v>-5.1582</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.8487</v>
+        <v>-4.1089</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.8396</v>
+        <v>-1.0492</v>
       </c>
       <c r="P12" t="n">
-        <v>0.195</v>
+        <v>-9.999999999998899e-05</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.8495</v>
+        <v>-3.8997</v>
       </c>
       <c r="R12" t="n">
-        <v>6.0445</v>
+        <v>3.8996</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8869</v>
+        <v>-0.7323999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2231</v>
+        <v>-0.8031</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3362</v>
+        <v>0.07069999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.4401</v>
+        <v>-1.287</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2786</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.7187</v>
+        <v>-1.287</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. MONES RIERA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1411,222 +1411,66 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.3385</v>
+        <v>-54.4042</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.863799999999999</v>
+        <v>-13.7102</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.4747</v>
+        <v>-40.69409999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.319000000000001</v>
+        <v>-55.2869</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.2523</v>
+        <v>-42.58819999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.0668</v>
+        <v>-12.699</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.1608</v>
+        <v>11.1221</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.1434</v>
+        <v>6.089700000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.0174</v>
+        <v>5.032</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.1582</v>
+        <v>-66.4092</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.1089</v>
+        <v>-48.6777</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0492</v>
+        <v>-17.7311</v>
       </c>
       <c r="P13" t="n">
-        <v>-9.999999999998899e-05</v>
+        <v>9.99999999995449e-05</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.8997</v>
+        <v>-53.62110000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>3.8996</v>
+        <v>53.62130000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7323999999999999</v>
+        <v>0.9364999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8031</v>
+        <v>-5.203400000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.07069999999999999</v>
+        <v>6.1393</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.287</v>
+        <v>-0.05300000000000171</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>33.9921</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.287</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>P. OSES BERNALDEZ</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>IREN BCBADAJOZ</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-13.0681</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-5.4754</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-7.5929</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-6.8119</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-4.620200000000001</v>
-      </c>
-      <c r="I14" t="n">
-        <v>-2.1918</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-1.4047</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-1.3313</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-0.07339999999999991</v>
-      </c>
-      <c r="M14" t="n">
-        <v>-5.4071</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-3.2888</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-2.1183</v>
-      </c>
-      <c r="P14" t="n">
-        <v>-3.1197</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-6.8245</v>
-      </c>
-      <c r="R14" t="n">
-        <v>3.7048</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.9243</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.8362000000000001</v>
-      </c>
-      <c r="V14" t="n">
-        <v>-4.0607</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.6658</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-6.7264</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>IREN BCBADAJOZ</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-54.4041</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-13.7103</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-40.69409999999999</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-55.2871</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-42.58839999999999</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-12.6993</v>
-      </c>
-      <c r="J15" t="n">
-        <v>11.122</v>
-      </c>
-      <c r="K15" t="n">
-        <v>6.089700000000001</v>
-      </c>
-      <c r="L15" t="n">
-        <v>5.032000000000002</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-66.4092</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-48.6777</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-17.7311</v>
-      </c>
-      <c r="P15" t="n">
-        <v>9.999999999932285e-05</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-53.62110000000001</v>
-      </c>
-      <c r="R15" t="n">
-        <v>53.6213</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.9365</v>
-      </c>
-      <c r="T15" t="n">
-        <v>-5.2034</v>
-      </c>
-      <c r="U15" t="n">
-        <v>6.1393</v>
-      </c>
-      <c r="V15" t="n">
-        <v>-0.05300000000000082</v>
-      </c>
-      <c r="W15" t="n">
-        <v>33.9921</v>
-      </c>
-      <c r="X15" t="n">
         <v>-34.0453</v>
       </c>
     </row>
